--- a/src/test/resources/excel/1. Irregular Verb.xlsx
+++ b/src/test/resources/excel/1. Irregular Verb.xlsx
@@ -7535,6 +7535,125 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>671400</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>389880</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="Image 1" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11908080" y="1463040"/>
+          <a:ext cx="671400" cy="389880"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>547560</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>384840</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="Image 2" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11908080" y="2089800"/>
+          <a:ext cx="547560" cy="384840"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>639720</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>29520</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Image 3" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId3"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11908080" y="0"/>
+          <a:ext cx="639720" cy="192240"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
   <a:themeElements>
@@ -7803,7 +7922,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="49.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
         <v>27</v>
       </c>
@@ -7820,7 +7939,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="30.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
         <v>31</v>
       </c>
@@ -8724,6 +8843,7 @@
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
